--- a/artfynd/A 22714-2026 artfynd.xlsx
+++ b/artfynd/A 22714-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133845685</v>
+        <v>133846502</v>
       </c>
       <c r="B2" t="n">
         <v>79117</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500361</v>
+        <v>500435</v>
       </c>
       <c r="R2" t="n">
-        <v>6821594</v>
+        <v>6821552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,57 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133858160</v>
+        <v>133845685</v>
       </c>
       <c r="B3" t="n">
-        <v>99181</v>
+        <v>79117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500374</v>
+        <v>500361</v>
       </c>
       <c r="R3" t="n">
-        <v>6821632</v>
+        <v>6821594</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,18 +845,12 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -984,45 +966,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133846502</v>
+        <v>133858160</v>
       </c>
       <c r="B5" t="n">
-        <v>79117</v>
+        <v>99181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500435</v>
+        <v>500374</v>
       </c>
       <c r="R5" t="n">
-        <v>6821552</v>
+        <v>6821632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,12 +1051,18 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1081,45 +1081,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133852574</v>
+        <v>133851617</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500730</v>
+        <v>500630</v>
       </c>
       <c r="R6" t="n">
-        <v>6821378</v>
+        <v>6821422</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856485</v>
+        <v>133853120</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,16 +1194,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1209,19 +1214,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501199</v>
+        <v>500879</v>
       </c>
       <c r="R7" t="n">
-        <v>6821619</v>
+        <v>6821386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,11 +1259,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 bild på ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,50 +1285,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133851617</v>
+        <v>133852574</v>
       </c>
       <c r="B8" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500630</v>
+        <v>500730</v>
       </c>
       <c r="R8" t="n">
-        <v>6821422</v>
+        <v>6821378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133851508</v>
+        <v>133854973</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>79117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1393,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500597</v>
+        <v>501022</v>
       </c>
       <c r="R9" t="n">
-        <v>6821419</v>
+        <v>6821451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133853120</v>
+        <v>133851508</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1520,7 +1510,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1529,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500879</v>
+        <v>500597</v>
       </c>
       <c r="R10" t="n">
-        <v>6821386</v>
+        <v>6821419</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,10 +1581,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133854973</v>
+        <v>133856485</v>
       </c>
       <c r="B11" t="n">
-        <v>79117</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,34 +1592,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501022</v>
+        <v>501199</v>
       </c>
       <c r="R11" t="n">
-        <v>6821451</v>
+        <v>6821619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1657,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 bild på ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,38 +1688,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133852640</v>
+        <v>133852481</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500730</v>
+        <v>500740</v>
       </c>
       <c r="R12" t="n">
-        <v>6821378</v>
+        <v>6821392</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,11 +1764,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,10 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133855212</v>
+        <v>133855410</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,39 +1801,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501139</v>
+        <v>501114</v>
       </c>
       <c r="R13" t="n">
-        <v>6821446</v>
+        <v>6821514</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1887,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133852481</v>
+        <v>133855212</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
@@ -1928,19 +1918,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500740</v>
+        <v>501139</v>
       </c>
       <c r="R14" t="n">
-        <v>6821392</v>
+        <v>6821446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,45 +1989,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133852466</v>
+        <v>133852640</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500740</v>
+        <v>500730</v>
       </c>
       <c r="R15" t="n">
-        <v>6821392</v>
+        <v>6821378</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,6 +2065,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2096,7 +2096,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133855410</v>
+        <v>133852466</v>
       </c>
       <c r="B16" t="n">
         <v>79359</v>
@@ -2127,14 +2127,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501114</v>
+        <v>500740</v>
       </c>
       <c r="R16" t="n">
-        <v>6821514</v>
+        <v>6821392</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133854164</v>
+        <v>133846935</v>
       </c>
       <c r="B18" t="n">
-        <v>79117</v>
+        <v>79949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,34 +2301,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500888</v>
+        <v>500425</v>
       </c>
       <c r="R18" t="n">
-        <v>6821439</v>
+        <v>6821526</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133854807</v>
+        <v>133854164</v>
       </c>
       <c r="B19" t="n">
         <v>79117</v>
@@ -2418,14 +2418,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501029</v>
+        <v>500888</v>
       </c>
       <c r="R19" t="n">
-        <v>6821374</v>
+        <v>6821439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133846935</v>
+        <v>133854807</v>
       </c>
       <c r="B20" t="n">
-        <v>79949</v>
+        <v>79117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500425</v>
+        <v>501029</v>
       </c>
       <c r="R20" t="n">
-        <v>6821526</v>
+        <v>6821374</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133856112</v>
+        <v>133851599</v>
       </c>
       <c r="B21" t="n">
-        <v>79949</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,34 +2592,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501165</v>
+        <v>500630</v>
       </c>
       <c r="R21" t="n">
-        <v>6821617</v>
+        <v>6821422</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133851599</v>
+        <v>133856112</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>79949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2689,39 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500630</v>
+        <v>501165</v>
       </c>
       <c r="R22" t="n">
-        <v>6821422</v>
+        <v>6821617</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133855381</v>
+        <v>133854813</v>
       </c>
       <c r="B23" t="n">
         <v>79359</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501130</v>
+        <v>501029</v>
       </c>
       <c r="R23" t="n">
-        <v>6821512</v>
+        <v>6821374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133854813</v>
+        <v>133851939</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,34 +2888,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501029</v>
+        <v>500642</v>
       </c>
       <c r="R24" t="n">
-        <v>6821374</v>
+        <v>6821414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,10 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133851939</v>
+        <v>133855381</v>
       </c>
       <c r="B25" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2985,34 +2985,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500642</v>
+        <v>501130</v>
       </c>
       <c r="R25" t="n">
-        <v>6821414</v>
+        <v>6821512</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3168,50 +3168,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133852928</v>
+        <v>133846946</v>
       </c>
       <c r="B27" t="n">
-        <v>8460</v>
+        <v>79117</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500811</v>
+        <v>500425</v>
       </c>
       <c r="R27" t="n">
-        <v>6821382</v>
+        <v>6821526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,45 +3265,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133856409</v>
+        <v>133852928</v>
       </c>
       <c r="B28" t="n">
-        <v>79117</v>
+        <v>8460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501224</v>
+        <v>500811</v>
       </c>
       <c r="R28" t="n">
-        <v>6821584</v>
+        <v>6821382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133855774</v>
+        <v>133847753</v>
       </c>
       <c r="B29" t="n">
-        <v>57972</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3378,39 +3378,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501116</v>
+        <v>500517</v>
       </c>
       <c r="R29" t="n">
-        <v>6821550</v>
+        <v>6821443</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3566,10 +3561,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133846946</v>
+        <v>133855774</v>
       </c>
       <c r="B31" t="n">
-        <v>79117</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3577,34 +3572,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500425</v>
+        <v>501116</v>
       </c>
       <c r="R31" t="n">
-        <v>6821526</v>
+        <v>6821550</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133847753</v>
+        <v>133856409</v>
       </c>
       <c r="B32" t="n">
-        <v>79454</v>
+        <v>79117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,34 +3674,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500517</v>
+        <v>501224</v>
       </c>
       <c r="R32" t="n">
-        <v>6821443</v>
+        <v>6821584</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,38 +3760,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133852978</v>
+        <v>133852416</v>
       </c>
       <c r="B33" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500823</v>
+        <v>500711</v>
       </c>
       <c r="R33" t="n">
-        <v>6821399</v>
+        <v>6821391</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,38 +3862,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133852416</v>
+        <v>133852978</v>
       </c>
       <c r="B34" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500711</v>
+        <v>500823</v>
       </c>
       <c r="R34" t="n">
-        <v>6821391</v>
+        <v>6821399</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133846233</v>
+        <v>133853225</v>
       </c>
       <c r="B37" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4179,34 +4179,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500417</v>
+        <v>500909</v>
       </c>
       <c r="R37" t="n">
-        <v>6821546</v>
+        <v>6821393</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133846685</v>
+        <v>133855962</v>
       </c>
       <c r="B38" t="n">
-        <v>79949</v>
+        <v>79359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4276,34 +4276,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500433</v>
+        <v>501140</v>
       </c>
       <c r="R38" t="n">
-        <v>6821519</v>
+        <v>6821577</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,45 +4362,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133855962</v>
+        <v>133852488</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501140</v>
+        <v>500740</v>
       </c>
       <c r="R39" t="n">
-        <v>6821577</v>
+        <v>6821392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4459,10 +4464,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133856104</v>
+        <v>133854192</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4470,34 +4475,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501165</v>
+        <v>500888</v>
       </c>
       <c r="R40" t="n">
-        <v>6821617</v>
+        <v>6821439</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4530,11 +4540,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På högstubbe 6 m hög + vedfl</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4561,10 +4566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133853225</v>
+        <v>133853199</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4572,21 +4577,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4658,50 +4663,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133852488</v>
+        <v>133856200</v>
       </c>
       <c r="B42" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500740</v>
+        <v>501179</v>
       </c>
       <c r="R42" t="n">
-        <v>6821392</v>
+        <v>6821539</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133856200</v>
+        <v>133856104</v>
       </c>
       <c r="B43" t="n">
-        <v>79359</v>
+        <v>78762</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>501179</v>
+        <v>501165</v>
       </c>
       <c r="R43" t="n">
-        <v>6821539</v>
+        <v>6821617</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4831,6 +4831,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På högstubbe 6 m hög + vedfl</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4857,10 +4862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133854720</v>
+        <v>133846233</v>
       </c>
       <c r="B44" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4868,34 +4873,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500987</v>
+        <v>500417</v>
       </c>
       <c r="R44" t="n">
-        <v>6821382</v>
+        <v>6821546</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,10 +4959,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133853199</v>
+        <v>133846685</v>
       </c>
       <c r="B45" t="n">
-        <v>79117</v>
+        <v>79949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4965,34 +4970,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500909</v>
+        <v>500433</v>
       </c>
       <c r="R45" t="n">
-        <v>6821393</v>
+        <v>6821519</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5051,10 +5056,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133854192</v>
+        <v>133854720</v>
       </c>
       <c r="B46" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5062,39 +5067,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500888</v>
+        <v>500987</v>
       </c>
       <c r="R46" t="n">
-        <v>6821439</v>
+        <v>6821382</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5153,38 +5153,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133857269</v>
+        <v>133855779</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>8460</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>501128</v>
+        <v>501116</v>
       </c>
       <c r="R47" t="n">
-        <v>6821630</v>
+        <v>6821550</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5229,11 +5229,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5260,38 +5255,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133855779</v>
+        <v>133857269</v>
       </c>
       <c r="B48" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5300,10 +5295,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>501116</v>
+        <v>501128</v>
       </c>
       <c r="R48" t="n">
-        <v>6821550</v>
+        <v>6821630</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5336,6 +5331,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5362,10 +5362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133851309</v>
+        <v>133856331</v>
       </c>
       <c r="B49" t="n">
-        <v>79949</v>
+        <v>79117</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,34 +5373,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500555</v>
+        <v>501222</v>
       </c>
       <c r="R49" t="n">
-        <v>6821389</v>
+        <v>6821558</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133855763</v>
+        <v>133851309</v>
       </c>
       <c r="B50" t="n">
-        <v>79117</v>
+        <v>79949</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,34 +5470,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>501114</v>
+        <v>500555</v>
       </c>
       <c r="R50" t="n">
-        <v>6821514</v>
+        <v>6821389</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,11 +5530,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Bild högstubbe kolad</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5561,7 +5556,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133856331</v>
+        <v>133855763</v>
       </c>
       <c r="B51" t="n">
         <v>79117</v>
@@ -5596,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>501222</v>
+        <v>501114</v>
       </c>
       <c r="R51" t="n">
-        <v>6821558</v>
+        <v>6821514</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5632,6 +5627,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Bild högstubbe kolad</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5658,10 +5658,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133846087</v>
+        <v>133847772</v>
       </c>
       <c r="B52" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5669,21 +5669,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500414</v>
+        <v>500517</v>
       </c>
       <c r="R52" t="n">
-        <v>6821563</v>
+        <v>6821443</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,10 +5755,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133847772</v>
+        <v>133846087</v>
       </c>
       <c r="B53" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5766,21 +5766,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500517</v>
+        <v>500414</v>
       </c>
       <c r="R53" t="n">
-        <v>6821443</v>
+        <v>6821563</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,50 +5852,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133854768</v>
+        <v>133856593</v>
       </c>
       <c r="B54" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>500987</v>
+        <v>501186</v>
       </c>
       <c r="R54" t="n">
-        <v>6821382</v>
+        <v>6821653</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6056,10 +6051,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133856593</v>
+        <v>133852937</v>
       </c>
       <c r="B56" t="n">
-        <v>79359</v>
+        <v>57972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6067,34 +6062,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>501186</v>
+        <v>500811</v>
       </c>
       <c r="R56" t="n">
-        <v>6821653</v>
+        <v>6821382</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6153,47 +6153,47 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133852937</v>
+        <v>133854768</v>
       </c>
       <c r="B57" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500811</v>
+        <v>500987</v>
       </c>
       <c r="R57" t="n">
         <v>6821382</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133854289</v>
+        <v>133855068</v>
       </c>
       <c r="B58" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6266,34 +6266,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500949</v>
+        <v>501058</v>
       </c>
       <c r="R58" t="n">
-        <v>6821371</v>
+        <v>6821468</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,10 +6352,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133855068</v>
+        <v>133846039</v>
       </c>
       <c r="B59" t="n">
-        <v>79117</v>
+        <v>78762</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6363,34 +6363,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>501058</v>
+        <v>500405</v>
       </c>
       <c r="R59" t="n">
-        <v>6821468</v>
+        <v>6821589</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6449,7 +6449,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133856528</v>
+        <v>133854289</v>
       </c>
       <c r="B60" t="n">
         <v>79359</v>
@@ -6480,14 +6480,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>501211</v>
+        <v>500949</v>
       </c>
       <c r="R60" t="n">
-        <v>6821636</v>
+        <v>6821371</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133855921</v>
+        <v>133856528</v>
       </c>
       <c r="B61" t="n">
         <v>79359</v>
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>501116</v>
+        <v>501211</v>
       </c>
       <c r="R61" t="n">
-        <v>6821550</v>
+        <v>6821636</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6643,10 +6643,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133846039</v>
+        <v>133855921</v>
       </c>
       <c r="B62" t="n">
-        <v>78762</v>
+        <v>79359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6654,34 +6654,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>500405</v>
+        <v>501116</v>
       </c>
       <c r="R62" t="n">
-        <v>6821589</v>
+        <v>6821550</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7138,50 +7138,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133852332</v>
+        <v>133856233</v>
       </c>
       <c r="B67" t="n">
-        <v>8460</v>
+        <v>79117</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>500711</v>
+        <v>501185</v>
       </c>
       <c r="R67" t="n">
-        <v>6821391</v>
+        <v>6821508</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7240,45 +7235,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133856233</v>
+        <v>133852433</v>
       </c>
       <c r="B68" t="n">
-        <v>79117</v>
+        <v>8460</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>501185</v>
+        <v>500711</v>
       </c>
       <c r="R68" t="n">
-        <v>6821508</v>
+        <v>6821391</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,45 +7628,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133852120</v>
+        <v>133857082</v>
       </c>
       <c r="B72" t="n">
-        <v>79949</v>
+        <v>99181</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500644</v>
+        <v>501145</v>
       </c>
       <c r="R72" t="n">
-        <v>6821430</v>
+        <v>6821667</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7703,7 +7715,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7712,6 +7724,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7730,57 +7743,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133857082</v>
+        <v>133852120</v>
       </c>
       <c r="B73" t="n">
-        <v>99181</v>
+        <v>79949</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>501145</v>
+        <v>500644</v>
       </c>
       <c r="R73" t="n">
-        <v>6821667</v>
+        <v>6821430</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,7 +7818,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7826,7 +7827,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7942,45 +7942,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133847290</v>
+        <v>133856447</v>
       </c>
       <c r="B75" t="n">
-        <v>79949</v>
+        <v>8460</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500507</v>
+        <v>501224</v>
       </c>
       <c r="R75" t="n">
-        <v>6821508</v>
+        <v>6821584</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8039,7 +8044,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133853734</v>
+        <v>133855191</v>
       </c>
       <c r="B76" t="n">
         <v>79359</v>
@@ -8070,14 +8075,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500871</v>
+        <v>501114</v>
       </c>
       <c r="R76" t="n">
-        <v>6821435</v>
+        <v>6821428</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8110,11 +8115,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8141,35 +8141,40 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133853083</v>
+        <v>133853130</v>
       </c>
       <c r="B77" t="n">
-        <v>79117</v>
+        <v>8460</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
@@ -8238,50 +8243,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133856447</v>
+        <v>133853083</v>
       </c>
       <c r="B78" t="n">
-        <v>8460</v>
+        <v>79117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>501224</v>
+        <v>500879</v>
       </c>
       <c r="R78" t="n">
-        <v>6821584</v>
+        <v>6821386</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8340,50 +8340,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133853130</v>
+        <v>133853734</v>
       </c>
       <c r="B79" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500879</v>
+        <v>500871</v>
       </c>
       <c r="R79" t="n">
-        <v>6821386</v>
+        <v>6821435</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8416,6 +8411,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8442,10 +8442,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133855191</v>
+        <v>133847290</v>
       </c>
       <c r="B80" t="n">
-        <v>79359</v>
+        <v>79949</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8453,34 +8453,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>501114</v>
+        <v>500507</v>
       </c>
       <c r="R80" t="n">
-        <v>6821428</v>
+        <v>6821508</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133847145</v>
+        <v>133852209</v>
       </c>
       <c r="B84" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8846,34 +8846,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500474</v>
+        <v>500674</v>
       </c>
       <c r="R84" t="n">
-        <v>6821498</v>
+        <v>6821410</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8932,7 +8932,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133846667</v>
+        <v>133854572</v>
       </c>
       <c r="B85" t="n">
         <v>79117</v>
@@ -8963,14 +8963,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500433</v>
+        <v>500960</v>
       </c>
       <c r="R85" t="n">
-        <v>6821519</v>
+        <v>6821382</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,10 +9029,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133846609</v>
+        <v>133856347</v>
       </c>
       <c r="B86" t="n">
-        <v>79949</v>
+        <v>79359</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9040,34 +9040,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>500445</v>
+        <v>501222</v>
       </c>
       <c r="R86" t="n">
-        <v>6821534</v>
+        <v>6821558</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133852209</v>
+        <v>133846667</v>
       </c>
       <c r="B87" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9137,34 +9137,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500674</v>
+        <v>500433</v>
       </c>
       <c r="R87" t="n">
-        <v>6821410</v>
+        <v>6821519</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133856347</v>
+        <v>133846609</v>
       </c>
       <c r="B88" t="n">
-        <v>79359</v>
+        <v>79949</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,34 +9234,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>501222</v>
+        <v>500445</v>
       </c>
       <c r="R88" t="n">
-        <v>6821558</v>
+        <v>6821534</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133854572</v>
+        <v>133847145</v>
       </c>
       <c r="B89" t="n">
         <v>79117</v>
@@ -9351,14 +9351,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500960</v>
+        <v>500474</v>
       </c>
       <c r="R89" t="n">
-        <v>6821382</v>
+        <v>6821498</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 22714-2026 artfynd.xlsx
+++ b/artfynd/A 22714-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133846502</v>
+        <v>133845685</v>
       </c>
       <c r="B2" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500435</v>
+        <v>500361</v>
       </c>
       <c r="R2" t="n">
-        <v>6821552</v>
+        <v>6821594</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133845685</v>
+        <v>133846502</v>
       </c>
       <c r="B3" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500361</v>
+        <v>500435</v>
       </c>
       <c r="R3" t="n">
-        <v>6821594</v>
+        <v>6821552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>133856288</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133858160</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,50 +1081,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133851617</v>
+        <v>133852574</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500630</v>
+        <v>500730</v>
       </c>
       <c r="R6" t="n">
-        <v>6821422</v>
+        <v>6821378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133853120</v>
+        <v>133856485</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,16 +1189,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1214,19 +1209,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500879</v>
+        <v>501199</v>
       </c>
       <c r="R7" t="n">
-        <v>6821386</v>
+        <v>6821619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,6 +1254,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 bild på ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,45 +1285,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133852574</v>
+        <v>133851617</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500730</v>
+        <v>500630</v>
       </c>
       <c r="R8" t="n">
-        <v>6821378</v>
+        <v>6821422</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133854973</v>
+        <v>133851508</v>
       </c>
       <c r="B9" t="n">
-        <v>79117</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501022</v>
+        <v>500597</v>
       </c>
       <c r="R9" t="n">
-        <v>6821451</v>
+        <v>6821419</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1489,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133851508</v>
+        <v>133853120</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1510,7 +1520,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1519,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500597</v>
+        <v>500879</v>
       </c>
       <c r="R10" t="n">
-        <v>6821419</v>
+        <v>6821386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133856485</v>
+        <v>133854973</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,39 +1602,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501199</v>
+        <v>501022</v>
       </c>
       <c r="R11" t="n">
-        <v>6821619</v>
+        <v>6821451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 bild på ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133852481</v>
+        <v>133855212</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
@@ -1719,19 +1719,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500740</v>
+        <v>501139</v>
       </c>
       <c r="R12" t="n">
-        <v>6821392</v>
+        <v>6821446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,45 +1790,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133855410</v>
+        <v>133852640</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501114</v>
+        <v>500730</v>
       </c>
       <c r="R13" t="n">
-        <v>6821514</v>
+        <v>6821378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,7 +1897,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133855212</v>
+        <v>133852481</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
@@ -1918,19 +1928,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501139</v>
+        <v>500740</v>
       </c>
       <c r="R14" t="n">
-        <v>6821446</v>
+        <v>6821392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,50 +1999,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133852640</v>
+        <v>133852466</v>
       </c>
       <c r="B15" t="n">
-        <v>57162</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500730</v>
+        <v>500740</v>
       </c>
       <c r="R15" t="n">
-        <v>6821378</v>
+        <v>6821392</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,11 +2070,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133852466</v>
+        <v>133855410</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,14 +2127,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500740</v>
+        <v>501114</v>
       </c>
       <c r="R16" t="n">
-        <v>6821392</v>
+        <v>6821514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133854211</v>
+        <v>133846935</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79956</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2204,34 +2204,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500888</v>
+        <v>500425</v>
       </c>
       <c r="R17" t="n">
-        <v>6821439</v>
+        <v>6821526</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133846935</v>
+        <v>133854211</v>
       </c>
       <c r="B18" t="n">
-        <v>79949</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,34 +2301,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500425</v>
+        <v>500888</v>
       </c>
       <c r="R18" t="n">
-        <v>6821526</v>
+        <v>6821439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
         <v>133854164</v>
       </c>
       <c r="B19" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>133854807</v>
       </c>
       <c r="B20" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133851599</v>
+        <v>133856112</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>79956</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,39 +2592,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500630</v>
+        <v>501165</v>
       </c>
       <c r="R21" t="n">
-        <v>6821422</v>
+        <v>6821617</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,10 +2678,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133856112</v>
+        <v>133851599</v>
       </c>
       <c r="B22" t="n">
-        <v>79949</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2689,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501165</v>
+        <v>500630</v>
       </c>
       <c r="R22" t="n">
-        <v>6821617</v>
+        <v>6821422</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133854813</v>
+        <v>133851939</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2791,34 +2791,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501029</v>
+        <v>500642</v>
       </c>
       <c r="R23" t="n">
-        <v>6821374</v>
+        <v>6821414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133851939</v>
+        <v>133855381</v>
       </c>
       <c r="B24" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,34 +2888,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500642</v>
+        <v>501130</v>
       </c>
       <c r="R24" t="n">
-        <v>6821414</v>
+        <v>6821512</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,10 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133855381</v>
+        <v>133852169</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,14 +3005,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>501130</v>
+        <v>500663</v>
       </c>
       <c r="R25" t="n">
-        <v>6821512</v>
+        <v>6821421</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,10 +3071,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133852169</v>
+        <v>133854813</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,14 +3102,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500663</v>
+        <v>501029</v>
       </c>
       <c r="R26" t="n">
-        <v>6821421</v>
+        <v>6821374</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3168,45 +3168,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133846946</v>
+        <v>133852928</v>
       </c>
       <c r="B27" t="n">
-        <v>79117</v>
+        <v>8460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500425</v>
+        <v>500811</v>
       </c>
       <c r="R27" t="n">
-        <v>6821526</v>
+        <v>6821382</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3265,50 +3270,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133852928</v>
+        <v>133855774</v>
       </c>
       <c r="B28" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500811</v>
+        <v>501116</v>
       </c>
       <c r="R28" t="n">
-        <v>6821382</v>
+        <v>6821550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,10 +3372,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133847753</v>
+        <v>133856409</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3378,34 +3383,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500517</v>
+        <v>501224</v>
       </c>
       <c r="R29" t="n">
-        <v>6821443</v>
+        <v>6821584</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,7 +3472,7 @@
         <v>133857282</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3561,10 +3566,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133855774</v>
+        <v>133846946</v>
       </c>
       <c r="B31" t="n">
-        <v>57972</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3572,39 +3577,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501116</v>
+        <v>500425</v>
       </c>
       <c r="R31" t="n">
-        <v>6821550</v>
+        <v>6821526</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133856409</v>
+        <v>133847753</v>
       </c>
       <c r="B32" t="n">
-        <v>79117</v>
+        <v>79461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,34 +3674,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501224</v>
+        <v>500517</v>
       </c>
       <c r="R32" t="n">
-        <v>6821584</v>
+        <v>6821443</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133852416</v>
+        <v>133856436</v>
       </c>
       <c r="B33" t="n">
         <v>57972</v>
@@ -3796,14 +3796,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500711</v>
+        <v>501224</v>
       </c>
       <c r="R33" t="n">
-        <v>6821391</v>
+        <v>6821584</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,50 +3964,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133856436</v>
+        <v>133851524</v>
       </c>
       <c r="B35" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>501224</v>
+        <v>500597</v>
       </c>
       <c r="R35" t="n">
-        <v>6821584</v>
+        <v>6821419</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,38 +4066,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133851524</v>
+        <v>133852416</v>
       </c>
       <c r="B36" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500597</v>
+        <v>500711</v>
       </c>
       <c r="R36" t="n">
-        <v>6821419</v>
+        <v>6821391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4171,7 +4171,7 @@
         <v>133853225</v>
       </c>
       <c r="B37" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,45 +4265,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133855962</v>
+        <v>133852488</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>501140</v>
+        <v>500740</v>
       </c>
       <c r="R38" t="n">
-        <v>6821577</v>
+        <v>6821392</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,50 +4367,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133852488</v>
+        <v>133856200</v>
       </c>
       <c r="B39" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500740</v>
+        <v>501179</v>
       </c>
       <c r="R39" t="n">
-        <v>6821392</v>
+        <v>6821539</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133854192</v>
+        <v>133855962</v>
       </c>
       <c r="B40" t="n">
-        <v>57972</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4475,39 +4475,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500888</v>
+        <v>501140</v>
       </c>
       <c r="R40" t="n">
-        <v>6821439</v>
+        <v>6821577</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4566,10 +4561,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133853199</v>
+        <v>133856104</v>
       </c>
       <c r="B41" t="n">
-        <v>79117</v>
+        <v>78769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,34 +4572,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500909</v>
+        <v>501165</v>
       </c>
       <c r="R41" t="n">
-        <v>6821393</v>
+        <v>6821617</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4637,6 +4632,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På högstubbe 6 m hög + vedfl</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4663,10 +4663,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133856200</v>
+        <v>133854720</v>
       </c>
       <c r="B42" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>501179</v>
+        <v>500987</v>
       </c>
       <c r="R42" t="n">
-        <v>6821539</v>
+        <v>6821382</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133856104</v>
+        <v>133853199</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4771,34 +4771,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>501165</v>
+        <v>500909</v>
       </c>
       <c r="R43" t="n">
-        <v>6821617</v>
+        <v>6821393</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4831,11 +4831,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På högstubbe 6 m hög + vedfl</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4862,10 +4857,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133846233</v>
+        <v>133854192</v>
       </c>
       <c r="B44" t="n">
-        <v>79117</v>
+        <v>57972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4873,34 +4868,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500417</v>
+        <v>500888</v>
       </c>
       <c r="R44" t="n">
-        <v>6821546</v>
+        <v>6821439</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133846685</v>
+        <v>133846233</v>
       </c>
       <c r="B45" t="n">
-        <v>79949</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4970,21 +4970,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500433</v>
+        <v>500417</v>
       </c>
       <c r="R45" t="n">
-        <v>6821519</v>
+        <v>6821546</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133854720</v>
+        <v>133846685</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>79956</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5067,34 +5067,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500987</v>
+        <v>500433</v>
       </c>
       <c r="R46" t="n">
-        <v>6821382</v>
+        <v>6821519</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5153,38 +5153,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133855779</v>
+        <v>133857269</v>
       </c>
       <c r="B47" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>501116</v>
+        <v>501128</v>
       </c>
       <c r="R47" t="n">
-        <v>6821550</v>
+        <v>6821630</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5229,6 +5229,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5255,38 +5260,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133857269</v>
+        <v>133855779</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>8460</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5295,10 +5300,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>501128</v>
+        <v>501116</v>
       </c>
       <c r="R48" t="n">
-        <v>6821630</v>
+        <v>6821550</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5331,11 +5336,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5362,10 +5362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133856331</v>
+        <v>133851309</v>
       </c>
       <c r="B49" t="n">
-        <v>79117</v>
+        <v>79956</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,34 +5373,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>501222</v>
+        <v>500555</v>
       </c>
       <c r="R49" t="n">
-        <v>6821558</v>
+        <v>6821389</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133851309</v>
+        <v>133855763</v>
       </c>
       <c r="B50" t="n">
-        <v>79949</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,34 +5470,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500555</v>
+        <v>501114</v>
       </c>
       <c r="R50" t="n">
-        <v>6821389</v>
+        <v>6821514</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,6 +5530,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Bild högstubbe kolad</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5556,10 +5561,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133855763</v>
+        <v>133856331</v>
       </c>
       <c r="B51" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5591,10 +5596,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>501114</v>
+        <v>501222</v>
       </c>
       <c r="R51" t="n">
-        <v>6821514</v>
+        <v>6821558</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,11 +5632,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Bild högstubbe kolad</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5658,10 +5658,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133847772</v>
+        <v>133846087</v>
       </c>
       <c r="B52" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5669,21 +5669,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500517</v>
+        <v>500414</v>
       </c>
       <c r="R52" t="n">
-        <v>6821443</v>
+        <v>6821563</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,10 +5755,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133846087</v>
+        <v>133847772</v>
       </c>
       <c r="B53" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5766,21 +5766,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500414</v>
+        <v>500517</v>
       </c>
       <c r="R53" t="n">
-        <v>6821563</v>
+        <v>6821443</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,10 +5852,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133856593</v>
+        <v>133852937</v>
       </c>
       <c r="B54" t="n">
-        <v>79359</v>
+        <v>57972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5863,34 +5863,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>501186</v>
+        <v>500811</v>
       </c>
       <c r="R54" t="n">
-        <v>6821653</v>
+        <v>6821382</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,7 +5954,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133855218</v>
+        <v>133854768</v>
       </c>
       <c r="B55" t="n">
         <v>8460</v>
@@ -5989,10 +5994,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>501139</v>
+        <v>500987</v>
       </c>
       <c r="R55" t="n">
-        <v>6821446</v>
+        <v>6821382</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6051,50 +6056,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133852937</v>
+        <v>133855218</v>
       </c>
       <c r="B56" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500811</v>
+        <v>501139</v>
       </c>
       <c r="R56" t="n">
-        <v>6821382</v>
+        <v>6821446</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6153,50 +6158,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133854768</v>
+        <v>133856593</v>
       </c>
       <c r="B57" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500987</v>
+        <v>501186</v>
       </c>
       <c r="R57" t="n">
-        <v>6821382</v>
+        <v>6821653</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
         <v>133855068</v>
       </c>
       <c r="B58" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6352,10 +6352,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133846039</v>
+        <v>133856528</v>
       </c>
       <c r="B59" t="n">
-        <v>78762</v>
+        <v>79366</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6363,34 +6363,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>500405</v>
+        <v>501211</v>
       </c>
       <c r="R59" t="n">
-        <v>6821589</v>
+        <v>6821636</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6449,10 +6449,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133854289</v>
+        <v>133855921</v>
       </c>
       <c r="B60" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6480,14 +6480,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>500949</v>
+        <v>501116</v>
       </c>
       <c r="R60" t="n">
-        <v>6821371</v>
+        <v>6821550</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6546,10 +6546,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133856528</v>
+        <v>133854289</v>
       </c>
       <c r="B61" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6577,14 +6577,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>501211</v>
+        <v>500949</v>
       </c>
       <c r="R61" t="n">
-        <v>6821636</v>
+        <v>6821371</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6643,10 +6643,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133855921</v>
+        <v>133846039</v>
       </c>
       <c r="B62" t="n">
-        <v>79359</v>
+        <v>78769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6654,34 +6654,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>501116</v>
+        <v>500405</v>
       </c>
       <c r="R62" t="n">
-        <v>6821550</v>
+        <v>6821589</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6740,53 +6740,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133849368</v>
+        <v>133845625</v>
       </c>
       <c r="B63" t="n">
-        <v>58658</v>
+        <v>78769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103044</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>500556</v>
+        <v>500361</v>
       </c>
       <c r="R63" t="n">
-        <v>6821433</v>
+        <v>6821594</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6842,48 +6837,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133845625</v>
+        <v>133849368</v>
       </c>
       <c r="B64" t="n">
-        <v>78762</v>
+        <v>58658</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6437</v>
+        <v>103044</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>500361</v>
+        <v>500556</v>
       </c>
       <c r="R64" t="n">
-        <v>6821594</v>
+        <v>6821433</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133857138</v>
+        <v>133846573</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7052,34 +7052,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>501144</v>
+        <v>500445</v>
       </c>
       <c r="R66" t="n">
-        <v>6821653</v>
+        <v>6821534</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7141,7 +7141,7 @@
         <v>133856233</v>
       </c>
       <c r="B67" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7235,50 +7235,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133852433</v>
+        <v>133857138</v>
       </c>
       <c r="B68" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500711</v>
+        <v>501144</v>
       </c>
       <c r="R68" t="n">
-        <v>6821391</v>
+        <v>6821653</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,45 +7332,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133846573</v>
+        <v>133852332</v>
       </c>
       <c r="B69" t="n">
-        <v>79117</v>
+        <v>8460</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500445</v>
+        <v>500711</v>
       </c>
       <c r="R69" t="n">
-        <v>6821534</v>
+        <v>6821391</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133854245</v>
+        <v>133855323</v>
       </c>
       <c r="B70" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7445,34 +7445,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500921</v>
+        <v>501118</v>
       </c>
       <c r="R70" t="n">
-        <v>6821418</v>
+        <v>6821479</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133855323</v>
+        <v>133854245</v>
       </c>
       <c r="B71" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7542,34 +7542,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>501118</v>
+        <v>500921</v>
       </c>
       <c r="R71" t="n">
-        <v>6821479</v>
+        <v>6821418</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7628,57 +7628,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133857082</v>
+        <v>133852120</v>
       </c>
       <c r="B72" t="n">
-        <v>99181</v>
+        <v>79956</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>501145</v>
+        <v>500644</v>
       </c>
       <c r="R72" t="n">
-        <v>6821667</v>
+        <v>6821430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7715,7 +7703,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7724,7 +7712,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7743,45 +7730,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133852120</v>
+        <v>133857082</v>
       </c>
       <c r="B73" t="n">
-        <v>79949</v>
+        <v>99188</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500644</v>
+        <v>501145</v>
       </c>
       <c r="R73" t="n">
-        <v>6821430</v>
+        <v>6821667</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7818,7 +7817,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7827,6 +7826,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>133845634</v>
       </c>
       <c r="B74" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8044,10 +8044,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133855191</v>
+        <v>133853083</v>
       </c>
       <c r="B76" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8055,34 +8055,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>501114</v>
+        <v>500879</v>
       </c>
       <c r="R76" t="n">
-        <v>6821428</v>
+        <v>6821386</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8141,50 +8141,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133853130</v>
+        <v>133853734</v>
       </c>
       <c r="B77" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500879</v>
+        <v>500871</v>
       </c>
       <c r="R77" t="n">
-        <v>6821386</v>
+        <v>6821435</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8217,6 +8212,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8243,35 +8243,40 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133853083</v>
+        <v>133853130</v>
       </c>
       <c r="B78" t="n">
-        <v>79117</v>
+        <v>8460</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
@@ -8340,10 +8345,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133853734</v>
+        <v>133855191</v>
       </c>
       <c r="B79" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8371,14 +8376,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500871</v>
+        <v>501114</v>
       </c>
       <c r="R79" t="n">
-        <v>6821435</v>
+        <v>6821428</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8411,11 +8416,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8445,7 +8445,7 @@
         <v>133847290</v>
       </c>
       <c r="B80" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>133857708</v>
       </c>
       <c r="B81" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>133855100</v>
       </c>
       <c r="B82" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>133856701</v>
       </c>
       <c r="B83" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>133852209</v>
       </c>
       <c r="B84" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>133854572</v>
       </c>
       <c r="B85" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>133856347</v>
       </c>
       <c r="B86" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133846667</v>
+        <v>133847145</v>
       </c>
       <c r="B87" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500433</v>
+        <v>500474</v>
       </c>
       <c r="R87" t="n">
-        <v>6821519</v>
+        <v>6821498</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133846609</v>
+        <v>133846667</v>
       </c>
       <c r="B88" t="n">
-        <v>79949</v>
+        <v>79124</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9234,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500445</v>
+        <v>500433</v>
       </c>
       <c r="R88" t="n">
-        <v>6821534</v>
+        <v>6821519</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133847145</v>
+        <v>133846609</v>
       </c>
       <c r="B89" t="n">
-        <v>79117</v>
+        <v>79956</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500474</v>
+        <v>500445</v>
       </c>
       <c r="R89" t="n">
-        <v>6821498</v>
+        <v>6821534</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9420,7 +9420,7 @@
         <v>133857006</v>
       </c>
       <c r="B90" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>133856572</v>
       </c>
       <c r="B91" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 22714-2026 artfynd.xlsx
+++ b/artfynd/A 22714-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133845685</v>
+        <v>133846767</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500361</v>
+        <v>500430</v>
       </c>
       <c r="R2" t="n">
-        <v>6821594</v>
+        <v>6821506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133846502</v>
+        <v>133847753</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500435</v>
+        <v>500517</v>
       </c>
       <c r="R3" t="n">
-        <v>6821552</v>
+        <v>6821443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133856288</v>
+        <v>133846867</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501207</v>
+        <v>500430</v>
       </c>
       <c r="R4" t="n">
-        <v>6821496</v>
+        <v>6821506</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133858160</v>
+        <v>133846087</v>
       </c>
       <c r="B5" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,46 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500374</v>
+        <v>500414</v>
       </c>
       <c r="R5" t="n">
-        <v>6821632</v>
+        <v>6821563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,18 +1043,12 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1081,14 +1067,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133852574</v>
+        <v>133852169</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1116,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500730</v>
+        <v>500663</v>
       </c>
       <c r="R6" t="n">
-        <v>6821378</v>
+        <v>6821421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,50 +1164,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133856485</v>
+        <v>133852209</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501199</v>
+        <v>500674</v>
       </c>
       <c r="R7" t="n">
-        <v>6821619</v>
+        <v>6821410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,11 +1235,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 bild på ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,50 +1261,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133851617</v>
+        <v>133852466</v>
       </c>
       <c r="B8" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500630</v>
+        <v>500740</v>
       </c>
       <c r="R8" t="n">
-        <v>6821422</v>
+        <v>6821392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,50 +1358,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133851508</v>
+        <v>133852574</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500597</v>
+        <v>500730</v>
       </c>
       <c r="R9" t="n">
-        <v>6821419</v>
+        <v>6821378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,50 +1455,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133853120</v>
+        <v>133853225</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500879</v>
+        <v>500909</v>
       </c>
       <c r="R10" t="n">
-        <v>6821386</v>
+        <v>6821393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,45 +1552,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133854973</v>
+        <v>133853734</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501022</v>
+        <v>500871</v>
       </c>
       <c r="R11" t="n">
-        <v>6821451</v>
+        <v>6821435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1623,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,50 +1654,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133855212</v>
+        <v>133854211</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501139</v>
+        <v>500888</v>
       </c>
       <c r="R12" t="n">
-        <v>6821446</v>
+        <v>6821439</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,50 +1751,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133852640</v>
+        <v>133854289</v>
       </c>
       <c r="B13" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500730</v>
+        <v>500949</v>
       </c>
       <c r="R13" t="n">
-        <v>6821378</v>
+        <v>6821371</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,11 +1822,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,50 +1848,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133852481</v>
+        <v>133854720</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500740</v>
+        <v>500987</v>
       </c>
       <c r="R14" t="n">
-        <v>6821392</v>
+        <v>6821382</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,14 +1945,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133852466</v>
+        <v>133854813</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2030,14 +1976,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500740</v>
+        <v>501029</v>
       </c>
       <c r="R15" t="n">
-        <v>6821392</v>
+        <v>6821374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,14 +2042,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133855410</v>
+        <v>133855100</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2131,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501114</v>
+        <v>501095</v>
       </c>
       <c r="R16" t="n">
-        <v>6821514</v>
+        <v>6821450</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,45 +2139,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133846935</v>
+        <v>133855191</v>
       </c>
       <c r="B17" t="n">
-        <v>79956</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500425</v>
+        <v>501114</v>
       </c>
       <c r="R17" t="n">
-        <v>6821526</v>
+        <v>6821428</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,14 +2236,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133854211</v>
+        <v>133855323</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2321,14 +2267,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500888</v>
+        <v>501118</v>
       </c>
       <c r="R18" t="n">
-        <v>6821439</v>
+        <v>6821479</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2387,45 +2333,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133854164</v>
+        <v>133855381</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500888</v>
+        <v>501130</v>
       </c>
       <c r="R19" t="n">
-        <v>6821439</v>
+        <v>6821512</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133854807</v>
+        <v>133855410</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2519,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501029</v>
+        <v>501114</v>
       </c>
       <c r="R20" t="n">
-        <v>6821374</v>
+        <v>6821514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,32 +2527,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133856112</v>
+        <v>133855785</v>
       </c>
       <c r="B21" t="n">
-        <v>79956</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2616,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501165</v>
+        <v>501116</v>
       </c>
       <c r="R21" t="n">
-        <v>6821617</v>
+        <v>6821550</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,50 +2624,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133851599</v>
+        <v>133855962</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500630</v>
+        <v>501140</v>
       </c>
       <c r="R22" t="n">
-        <v>6821422</v>
+        <v>6821577</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,45 +2721,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133851939</v>
+        <v>133856200</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500642</v>
+        <v>501179</v>
       </c>
       <c r="R23" t="n">
-        <v>6821414</v>
+        <v>6821539</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,14 +2818,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133855381</v>
+        <v>133856288</v>
       </c>
       <c r="B24" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2912,10 +2853,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501130</v>
+        <v>501207</v>
       </c>
       <c r="R24" t="n">
-        <v>6821512</v>
+        <v>6821496</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,14 +2915,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133852169</v>
+        <v>133856347</v>
       </c>
       <c r="B25" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3005,14 +2946,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500663</v>
+        <v>501222</v>
       </c>
       <c r="R25" t="n">
-        <v>6821421</v>
+        <v>6821558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,14 +3012,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133854813</v>
+        <v>133856528</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3106,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501029</v>
+        <v>501211</v>
       </c>
       <c r="R26" t="n">
-        <v>6821374</v>
+        <v>6821636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3168,50 +3109,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133852928</v>
+        <v>133856593</v>
       </c>
       <c r="B27" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500811</v>
+        <v>501186</v>
       </c>
       <c r="R27" t="n">
-        <v>6821382</v>
+        <v>6821653</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,50 +3206,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133855774</v>
+        <v>133856701</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501116</v>
+        <v>501176</v>
       </c>
       <c r="R28" t="n">
-        <v>6821550</v>
+        <v>6821691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,6 +3277,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bild gren gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3372,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133856409</v>
+        <v>133857138</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3407,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501224</v>
+        <v>501144</v>
       </c>
       <c r="R29" t="n">
-        <v>6821584</v>
+        <v>6821653</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3472,11 +3408,11 @@
         <v>133857282</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3566,42 +3502,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133846946</v>
+        <v>133857708</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500425</v>
+        <v>500890</v>
       </c>
       <c r="R31" t="n">
         <v>6821526</v>
@@ -3663,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133847753</v>
+        <v>133845625</v>
       </c>
       <c r="B32" t="n">
-        <v>79461</v>
+        <v>78776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>967</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3698,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500517</v>
+        <v>500361</v>
       </c>
       <c r="R32" t="n">
-        <v>6821443</v>
+        <v>6821594</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133856436</v>
+        <v>133846039</v>
       </c>
       <c r="B33" t="n">
-        <v>57972</v>
+        <v>78776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3771,39 +3707,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501224</v>
+        <v>500405</v>
       </c>
       <c r="R33" t="n">
-        <v>6821584</v>
+        <v>6821589</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,50 +3793,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133852978</v>
+        <v>133856104</v>
       </c>
       <c r="B34" t="n">
-        <v>8460</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500823</v>
+        <v>501165</v>
       </c>
       <c r="R34" t="n">
-        <v>6821399</v>
+        <v>6821617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3938,6 +3864,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På högstubbe 6 m hög + vedfl</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3964,10 +3895,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133851524</v>
+        <v>133851508</v>
       </c>
       <c r="B35" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3975,27 +3906,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4066,14 +3997,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133852416</v>
+        <v>133851599</v>
       </c>
       <c r="B36" t="n">
         <v>57972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4097,7 +4028,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4106,10 +4037,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500711</v>
+        <v>500630</v>
       </c>
       <c r="R36" t="n">
-        <v>6821391</v>
+        <v>6821422</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,45 +4099,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133853225</v>
+        <v>133852328</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500909</v>
+        <v>500711</v>
       </c>
       <c r="R37" t="n">
-        <v>6821393</v>
+        <v>6821391</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4265,10 +4201,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133852488</v>
+        <v>133852481</v>
       </c>
       <c r="B38" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4276,27 +4212,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4367,45 +4303,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133856200</v>
+        <v>133852937</v>
       </c>
       <c r="B39" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501179</v>
+        <v>500811</v>
       </c>
       <c r="R39" t="n">
-        <v>6821539</v>
+        <v>6821382</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4464,45 +4405,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133855962</v>
+        <v>133853120</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501140</v>
+        <v>500879</v>
       </c>
       <c r="R40" t="n">
-        <v>6821577</v>
+        <v>6821386</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4561,45 +4507,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133856104</v>
+        <v>133854192</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>57972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501165</v>
+        <v>500888</v>
       </c>
       <c r="R41" t="n">
-        <v>6821617</v>
+        <v>6821439</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4632,11 +4583,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På högstubbe 6 m hög + vedfl</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4663,45 +4609,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133854720</v>
+        <v>133855212</v>
       </c>
       <c r="B42" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500987</v>
+        <v>501139</v>
       </c>
       <c r="R42" t="n">
-        <v>6821382</v>
+        <v>6821446</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,45 +4711,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133853199</v>
+        <v>133855774</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>57972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500909</v>
+        <v>501116</v>
       </c>
       <c r="R43" t="n">
-        <v>6821393</v>
+        <v>6821550</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4857,14 +4813,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133854192</v>
+        <v>133856436</v>
       </c>
       <c r="B44" t="n">
         <v>57972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4888,19 +4844,19 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500888</v>
+        <v>501224</v>
       </c>
       <c r="R44" t="n">
-        <v>6821439</v>
+        <v>6821584</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4959,10 +4915,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133846233</v>
+        <v>133856485</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4970,34 +4926,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500417</v>
+        <v>501199</v>
       </c>
       <c r="R45" t="n">
-        <v>6821546</v>
+        <v>6821619</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5030,6 +4991,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 bild på ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5056,10 +5022,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133846685</v>
+        <v>133857243</v>
       </c>
       <c r="B46" t="n">
-        <v>79956</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5067,34 +5033,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500433</v>
+        <v>501128</v>
       </c>
       <c r="R46" t="n">
-        <v>6821519</v>
+        <v>6821630</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5127,6 +5098,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5153,50 +5129,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133857269</v>
+        <v>133852640</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>501128</v>
+        <v>500730</v>
       </c>
       <c r="R47" t="n">
-        <v>6821630</v>
+        <v>6821378</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5233,7 +5209,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5260,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133855779</v>
+        <v>133849368</v>
       </c>
       <c r="B48" t="n">
-        <v>8460</v>
+        <v>58658</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5271,42 +5247,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>501116</v>
+        <v>500556</v>
       </c>
       <c r="R48" t="n">
-        <v>6821550</v>
+        <v>6821433</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5362,45 +5338,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133851309</v>
+        <v>133851524</v>
       </c>
       <c r="B49" t="n">
-        <v>79956</v>
+        <v>8460</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500555</v>
+        <v>500597</v>
       </c>
       <c r="R49" t="n">
-        <v>6821389</v>
+        <v>6821419</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,45 +5440,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133855763</v>
+        <v>133851617</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>8460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>501114</v>
+        <v>500630</v>
       </c>
       <c r="R50" t="n">
-        <v>6821514</v>
+        <v>6821422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,11 +5516,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Bild högstubbe kolad</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5561,45 +5542,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133856331</v>
+        <v>133852332</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>8460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>501222</v>
+        <v>500711</v>
       </c>
       <c r="R51" t="n">
-        <v>6821558</v>
+        <v>6821391</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,45 +5644,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133846087</v>
+        <v>133852488</v>
       </c>
       <c r="B52" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500414</v>
+        <v>500740</v>
       </c>
       <c r="R52" t="n">
-        <v>6821563</v>
+        <v>6821392</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,45 +5746,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133847772</v>
+        <v>133852928</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>8460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500517</v>
+        <v>500811</v>
       </c>
       <c r="R53" t="n">
-        <v>6821443</v>
+        <v>6821382</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,38 +5848,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133852937</v>
+        <v>133852978</v>
       </c>
       <c r="B54" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5892,10 +5888,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>500811</v>
+        <v>500823</v>
       </c>
       <c r="R54" t="n">
-        <v>6821382</v>
+        <v>6821399</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5954,7 +5950,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133854768</v>
+        <v>133853130</v>
       </c>
       <c r="B55" t="n">
         <v>8460</v>
@@ -5990,14 +5986,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500987</v>
+        <v>500879</v>
       </c>
       <c r="R55" t="n">
-        <v>6821382</v>
+        <v>6821386</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,7 +6052,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133855218</v>
+        <v>133854205</v>
       </c>
       <c r="B56" t="n">
         <v>8460</v>
@@ -6092,14 +6088,14 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>501139</v>
+        <v>500888</v>
       </c>
       <c r="R56" t="n">
-        <v>6821446</v>
+        <v>6821439</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6158,45 +6154,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133856593</v>
+        <v>133854768</v>
       </c>
       <c r="B57" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>501186</v>
+        <v>500987</v>
       </c>
       <c r="R57" t="n">
-        <v>6821653</v>
+        <v>6821382</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6255,45 +6256,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133855068</v>
+        <v>133855218</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>8460</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>501058</v>
+        <v>501139</v>
       </c>
       <c r="R58" t="n">
-        <v>6821468</v>
+        <v>6821446</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,45 +6358,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133856528</v>
+        <v>133855779</v>
       </c>
       <c r="B59" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>501211</v>
+        <v>501116</v>
       </c>
       <c r="R59" t="n">
-        <v>6821636</v>
+        <v>6821550</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6449,45 +6460,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133855921</v>
+        <v>133856447</v>
       </c>
       <c r="B60" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>501116</v>
+        <v>501224</v>
       </c>
       <c r="R60" t="n">
-        <v>6821550</v>
+        <v>6821584</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6546,45 +6562,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133854289</v>
+        <v>133857006</v>
       </c>
       <c r="B61" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>500949</v>
+        <v>501154</v>
       </c>
       <c r="R61" t="n">
-        <v>6821371</v>
+        <v>6821676</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6619,12 +6647,18 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Miljöbilder på sumpskog norr om fyndplats för knärot</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6643,45 +6677,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133846039</v>
+        <v>133857082</v>
       </c>
       <c r="B62" t="n">
-        <v>78769</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>500405</v>
+        <v>501145</v>
       </c>
       <c r="R62" t="n">
-        <v>6821589</v>
+        <v>6821667</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6716,12 +6762,18 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6740,45 +6792,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133845625</v>
+        <v>133858160</v>
       </c>
       <c r="B63" t="n">
-        <v>78769</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>500361</v>
+        <v>500374</v>
       </c>
       <c r="R63" t="n">
-        <v>6821594</v>
+        <v>6821632</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6813,12 +6877,18 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6837,53 +6907,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133849368</v>
+        <v>133845685</v>
       </c>
       <c r="B64" t="n">
-        <v>58658</v>
+        <v>79131</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103044</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>500556</v>
+        <v>500361</v>
       </c>
       <c r="R64" t="n">
-        <v>6821433</v>
+        <v>6821594</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6939,50 +7004,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133854205</v>
+        <v>133846233</v>
       </c>
       <c r="B65" t="n">
-        <v>8460</v>
+        <v>79131</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>500888</v>
+        <v>500417</v>
       </c>
       <c r="R65" t="n">
-        <v>6821439</v>
+        <v>6821546</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7041,10 +7101,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133846573</v>
+        <v>133846339</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7076,10 +7136,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>500445</v>
+        <v>500435</v>
       </c>
       <c r="R66" t="n">
-        <v>6821534</v>
+        <v>6821552</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7138,10 +7198,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133856233</v>
+        <v>133846573</v>
       </c>
       <c r="B67" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7169,14 +7229,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>501185</v>
+        <v>500445</v>
       </c>
       <c r="R67" t="n">
-        <v>6821508</v>
+        <v>6821534</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7235,10 +7295,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133857138</v>
+        <v>133846667</v>
       </c>
       <c r="B68" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7246,34 +7306,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>501144</v>
+        <v>500433</v>
       </c>
       <c r="R68" t="n">
-        <v>6821653</v>
+        <v>6821519</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7332,50 +7392,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133852332</v>
+        <v>133846719</v>
       </c>
       <c r="B69" t="n">
-        <v>8460</v>
+        <v>79131</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500711</v>
+        <v>500430</v>
       </c>
       <c r="R69" t="n">
-        <v>6821391</v>
+        <v>6821506</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7434,10 +7489,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133855323</v>
+        <v>133846889</v>
       </c>
       <c r="B70" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7445,34 +7500,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>501118</v>
+        <v>500424</v>
       </c>
       <c r="R70" t="n">
-        <v>6821479</v>
+        <v>6821513</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7531,10 +7586,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133854245</v>
+        <v>133846946</v>
       </c>
       <c r="B71" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7562,14 +7617,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500921</v>
+        <v>500425</v>
       </c>
       <c r="R71" t="n">
-        <v>6821418</v>
+        <v>6821526</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7628,10 +7683,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133852120</v>
+        <v>133847145</v>
       </c>
       <c r="B72" t="n">
-        <v>79956</v>
+        <v>79131</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7639,34 +7694,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500644</v>
+        <v>500474</v>
       </c>
       <c r="R72" t="n">
-        <v>6821430</v>
+        <v>6821498</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7699,11 +7754,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7730,57 +7780,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133857082</v>
+        <v>133847772</v>
       </c>
       <c r="B73" t="n">
-        <v>99188</v>
+        <v>79131</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>501145</v>
+        <v>500517</v>
       </c>
       <c r="R73" t="n">
-        <v>6821667</v>
+        <v>6821443</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7815,18 +7853,12 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7845,10 +7877,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133845634</v>
+        <v>133851396</v>
       </c>
       <c r="B74" t="n">
-        <v>79956</v>
+        <v>79131</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7856,34 +7888,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500361</v>
+        <v>500568</v>
       </c>
       <c r="R74" t="n">
-        <v>6821594</v>
+        <v>6821379</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7942,50 +7974,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133856447</v>
+        <v>133851939</v>
       </c>
       <c r="B75" t="n">
-        <v>8460</v>
+        <v>79131</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>501224</v>
+        <v>500642</v>
       </c>
       <c r="R75" t="n">
-        <v>6821584</v>
+        <v>6821414</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8047,7 +8074,7 @@
         <v>133853083</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8141,10 +8168,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133853734</v>
+        <v>133853199</v>
       </c>
       <c r="B77" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8152,21 +8179,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8176,10 +8203,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500871</v>
+        <v>500909</v>
       </c>
       <c r="R77" t="n">
-        <v>6821435</v>
+        <v>6821393</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8212,11 +8239,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8243,50 +8265,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133853130</v>
+        <v>133853803</v>
       </c>
       <c r="B78" t="n">
-        <v>8460</v>
+        <v>79131</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500879</v>
+        <v>500888</v>
       </c>
       <c r="R78" t="n">
-        <v>6821386</v>
+        <v>6821439</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8345,10 +8362,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133855191</v>
+        <v>133854245</v>
       </c>
       <c r="B79" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8356,34 +8373,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Orsatjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>501114</v>
+        <v>500921</v>
       </c>
       <c r="R79" t="n">
-        <v>6821428</v>
+        <v>6821418</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8442,10 +8459,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133847290</v>
+        <v>133854572</v>
       </c>
       <c r="B80" t="n">
-        <v>79956</v>
+        <v>79131</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8453,34 +8470,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500507</v>
+        <v>500960</v>
       </c>
       <c r="R80" t="n">
-        <v>6821508</v>
+        <v>6821382</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8539,10 +8556,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133857708</v>
+        <v>133854807</v>
       </c>
       <c r="B81" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8550,21 +8567,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8574,10 +8591,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>500890</v>
+        <v>501029</v>
       </c>
       <c r="R81" t="n">
-        <v>6821526</v>
+        <v>6821374</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8636,10 +8653,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133855100</v>
+        <v>133854973</v>
       </c>
       <c r="B82" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8647,21 +8664,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,10 +8688,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>501095</v>
+        <v>501022</v>
       </c>
       <c r="R82" t="n">
-        <v>6821450</v>
+        <v>6821451</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8733,10 +8750,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133856701</v>
+        <v>133855068</v>
       </c>
       <c r="B83" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8744,21 +8761,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8768,10 +8785,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>501176</v>
+        <v>501058</v>
       </c>
       <c r="R83" t="n">
-        <v>6821691</v>
+        <v>6821468</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8804,11 +8821,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Bild gren gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8835,10 +8847,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133852209</v>
+        <v>133855763</v>
       </c>
       <c r="B84" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8846,34 +8858,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Orsatjärnarna, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>500674</v>
+        <v>501114</v>
       </c>
       <c r="R84" t="n">
-        <v>6821410</v>
+        <v>6821514</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8906,6 +8918,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Bild högstubbe kolad</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8932,10 +8949,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133854572</v>
+        <v>133856233</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8967,10 +8984,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>500960</v>
+        <v>501185</v>
       </c>
       <c r="R85" t="n">
-        <v>6821382</v>
+        <v>6821508</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9029,10 +9046,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133856347</v>
+        <v>133856331</v>
       </c>
       <c r="B86" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9040,21 +9057,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9126,10 +9143,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133847145</v>
+        <v>133856409</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9157,14 +9174,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>500474</v>
+        <v>501224</v>
       </c>
       <c r="R87" t="n">
-        <v>6821498</v>
+        <v>6821584</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9223,10 +9240,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133846667</v>
+        <v>133856572</v>
       </c>
       <c r="B88" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9254,14 +9271,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Skarpberget, Dlr</t>
+          <t>Svartbäckskojan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>500433</v>
+        <v>501193</v>
       </c>
       <c r="R88" t="n">
-        <v>6821519</v>
+        <v>6821646</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9294,6 +9311,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Bild 2 stubbar</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,10 +9342,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133846609</v>
+        <v>133845634</v>
       </c>
       <c r="B89" t="n">
-        <v>79956</v>
+        <v>79963</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9355,10 +9377,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>500445</v>
+        <v>500361</v>
       </c>
       <c r="R89" t="n">
-        <v>6821534</v>
+        <v>6821594</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9417,57 +9439,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133857006</v>
+        <v>133846609</v>
       </c>
       <c r="B90" t="n">
-        <v>99188</v>
+        <v>79963</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>501154</v>
+        <v>500445</v>
       </c>
       <c r="R90" t="n">
-        <v>6821676</v>
+        <v>6821534</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9502,18 +9512,12 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Miljöbilder på sumpskog norr om fyndplats för knärot</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9532,10 +9536,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133856572</v>
+        <v>133846685</v>
       </c>
       <c r="B91" t="n">
-        <v>79124</v>
+        <v>79963</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9543,34 +9547,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Svartbäckskojan, Dlr</t>
+          <t>Skarpberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>501193</v>
+        <v>500433</v>
       </c>
       <c r="R91" t="n">
-        <v>6821646</v>
+        <v>6821519</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9605,11 +9609,6 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Bild 2 stubbar</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9631,6 +9630,787 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>133846725</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Skarpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>500430</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6821506</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>133846913</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Skarpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>500424</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6821513</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>133846935</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Skarpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>500425</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6821526</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>133847290</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Skarpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>500507</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6821508</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>133851309</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Orsatjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>500555</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6821389</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>133851405</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Orsatjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>500568</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6821379</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>133852120</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Orsatjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>500644</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6821430</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>133856112</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Svartbäckskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>501165</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6821617</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22714-2026 artfynd.xlsx
+++ b/artfynd/A 22714-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846767</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133847753</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846087</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852169</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852209</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852466</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852574</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853225</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853734</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854211</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854289</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854720</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854813</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855100</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855191</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855323</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855381</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855410</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855785</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855962</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856288</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3009,6 +3129,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856347</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3106,6 +3231,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856528</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3203,6 +3333,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856593</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3305,6 +3440,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856701</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3402,6 +3542,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133857138</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3499,6 +3644,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133857282</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3596,6 +3746,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133857708</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3693,6 +3848,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133845625</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3790,6 +3950,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846039</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3892,6 +4057,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856104</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3994,6 +4164,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851508</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4096,6 +4271,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851599</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4198,6 +4378,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852328</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4300,6 +4485,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852481</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4402,6 +4592,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852937</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4504,6 +4699,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853120</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4606,6 +4806,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854192</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4708,6 +4913,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855212</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4810,6 +5020,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855774</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4912,6 +5127,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856436</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5019,6 +5239,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856485</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5126,6 +5351,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133857243</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5233,6 +5463,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852640</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5335,6 +5570,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133849368</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5437,6 +5677,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851524</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5539,6 +5784,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851617</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5641,6 +5891,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852332</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5743,6 +5998,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852488</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5845,6 +6105,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852928</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5947,6 +6212,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852978</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6049,6 +6319,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853130</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6151,6 +6426,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854205</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6253,6 +6533,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854768</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6355,6 +6640,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855218</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6457,6 +6747,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855779</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6559,6 +6854,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856447</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6674,6 +6974,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133857006</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6789,6 +7094,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133857082</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6904,6 +7214,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133858160</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7001,6 +7316,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133845685</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7098,6 +7418,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846233</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7195,6 +7520,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846339</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7292,6 +7622,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846573</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7389,6 +7724,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846667</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7486,6 +7826,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846719</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7583,6 +7928,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846889</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7680,6 +8030,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846946</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7777,6 +8132,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133847145</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7874,6 +8234,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133847772</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7971,6 +8336,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851396</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8068,6 +8438,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851939</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8165,6 +8540,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853083</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8262,6 +8642,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853199</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8359,6 +8744,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853803</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8456,6 +8846,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854245</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8553,6 +8948,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854572</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8650,6 +9050,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854807</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8747,6 +9152,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133854973</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8844,6 +9254,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855068</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8946,6 +9361,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855763</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9043,6 +9463,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856233</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9140,6 +9565,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856331</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9237,6 +9667,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856409</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9339,6 +9774,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856572</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9436,6 +9876,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133845634</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9533,6 +9978,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846609</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9630,6 +10080,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846685</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9727,6 +10182,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846725</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9824,6 +10284,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846913</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9921,6 +10386,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133846935</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10018,6 +10488,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133847290</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10115,6 +10590,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851309</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10212,6 +10692,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851405</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10314,6 +10799,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133852120</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10411,8 +10901,113 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856112</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>